--- a/L12PJM.xlsx
+++ b/L12PJM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t/>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>PT</t>
   </si>
 </sst>
 </file>
@@ -497,7 +500,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/L12PJM.xlsx
+++ b/L12PJM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
   <si>
     <t/>
   </si>
@@ -38,9 +38,6 @@
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>PT</t>
   </si>
 </sst>
 </file>
@@ -500,7 +497,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
